--- a/(枠)◯年度一式/促進税原簿.xlsx
+++ b/(枠)◯年度一式/促進税原簿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\layhi\OneDrive\ドキュメント\日報月報他\(枠)◯年度一式\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{47D7E90B-C99B-47C7-B4E9-71F3058C564A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7784084-57C5-411E-8AC0-0C4D0F72D2C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="420" yWindow="765" windowWidth="16770" windowHeight="14715" tabRatio="937" firstSheet="12" activeTab="23" xr2:uid="{F879715F-57C6-4104-A4D9-BD89F6EC0AE8}"/>
+    <workbookView xWindow="540" yWindow="870" windowWidth="20670" windowHeight="14715" tabRatio="937" activeTab="12" xr2:uid="{F879715F-57C6-4104-A4D9-BD89F6EC0AE8}"/>
   </bookViews>
   <sheets>
     <sheet name="汚泥04" sheetId="11" r:id="rId1"/>
